--- a/inventories/baseline/lci-Salar-de-Pastos-Grandes.xlsx
+++ b/inventories/baseline/lci-Salar-de-Pastos-Grandes.xlsx
@@ -881,7 +881,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.01907839099273903</v>
+        <v>0.01907839099273902</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -898,7 +898,7 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>0.02474001677726592</v>
+        <v>0.02474001677726591</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -932,7 +932,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0003711002516589891</v>
+        <v>0.000371100251658989</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -1213,7 +1213,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.4827632504728835</v>
+        <v>0.4289507800736467</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1230,7 +1230,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.3965459369088957</v>
+        <v>0.4638115249079416</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.113471271489272</v>
+        <v>0.1327192604038043</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1264,7 +1264,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.1206908126182209</v>
+        <v>0.1072376950184117</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1379,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0005860508005212914</v>
+        <v>0.0005860508005212913</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1396,7 +1396,7 @@
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.9975896281979559</v>
+        <v>0.9975896281979558</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>3</v>
       </c>
       <c r="B89">
-        <v>0.04043689684428631</v>
+        <v>0.0404368968442863</v>
       </c>
       <c r="C89" t="s">
         <v>1</v>
@@ -1545,7 +1545,7 @@
         <v>47</v>
       </c>
       <c r="B90">
-        <v>0.9494538789446422</v>
+        <v>0.9494538789446421</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>10.30055600261943</v>
+        <v>11.59277504204272</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.01097600229787316</v>
+        <v>0.01235295701201273</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1877,7 +1877,7 @@
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-0.009300556002619429</v>
+        <v>-0.01059277504204272</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         <v>26</v>
       </c>
       <c r="B132">
-        <v>1.052631578947368</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -2009,7 +2009,7 @@
         <v>22</v>
       </c>
       <c r="B133">
-        <v>0.0005263157894736842</v>
+        <v>0.0005263157894736843</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2026,7 +2026,7 @@
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-0.05263157894736842</v>
+        <v>-0.05263157894736843</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2158,7 +2158,7 @@
         <v>22</v>
       </c>
       <c r="B147">
-        <v>4.251955821430681E-05</v>
+        <v>4.25195582143068E-05</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2720,7 +2720,7 @@
         <v>55</v>
       </c>
       <c r="B201">
-        <v>0.04918032776532028</v>
+        <v>0.03736084123536588</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -2737,7 +2737,7 @@
         <v>56</v>
       </c>
       <c r="B202">
-        <v>7.610773268446759E-10</v>
+        <v>5.781679477974383E-10</v>
       </c>
       <c r="D202" t="s">
         <v>57</v>
@@ -2754,7 +2754,7 @@
         <v>59</v>
       </c>
       <c r="B203">
-        <v>1.90269331711169E-11</v>
+        <v>1.445419869493596E-11</v>
       </c>
       <c r="D203" t="s">
         <v>60</v>
@@ -2771,7 +2771,7 @@
         <v>61</v>
       </c>
       <c r="B204">
-        <v>1.90269331711169E-11</v>
+        <v>1.445419869493596E-11</v>
       </c>
       <c r="D204" t="s">
         <v>60</v>
@@ -2822,7 +2822,7 @@
         <v>3</v>
       </c>
       <c r="B207">
-        <v>7.271285021171323</v>
+        <v>5.764109851722622</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>62</v>
       </c>
       <c r="B208">
-        <v>0.0003177405643643959</v>
+        <v>0.0002413781143529644</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2856,7 +2856,7 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>0.2479433291834605</v>
+        <v>0.1887647016120531</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2873,7 +2873,7 @@
         <v>45</v>
       </c>
       <c r="B210">
-        <v>6.553137554193747E-09</v>
+        <v>0.7481233129073279</v>
       </c>
       <c r="C210" t="s">
         <v>31</v>
@@ -2890,7 +2890,7 @@
         <v>64</v>
       </c>
       <c r="B211">
-        <v>0.01308831303431911</v>
+        <v>0.009942804522315114</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2907,7 +2907,7 @@
         <v>65</v>
       </c>
       <c r="B212">
-        <v>-5.30129177862933E-16</v>
+        <v>-4.027234658313606E-16</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2924,7 +2924,7 @@
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-0.007271285019066173</v>
+        <v>-0.005523780290175064</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
@@ -3022,7 +3022,7 @@
         <v>66</v>
       </c>
       <c r="B224">
-        <v>-0.0006900000000000001</v>
+        <v>-0.0006900000000000002</v>
       </c>
       <c r="D224" t="s">
         <v>11</v>
